--- a/03_数据/测试题库与验收记录表.xlsx
+++ b/03_数据/测试题库与验收记录表.xlsx
@@ -3896,12 +3896,12 @@
       <c r="E15" s="8" t="inlineStr"/>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否（待补）</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>已配置 GitHub Actions 每月1日核对语料（.github/workflows）</t>
+          <t>静态站点未配置平台级定时任务；_build/check.py 可作月度健康检查，待接入定时任务平台。</t>
         </is>
       </c>
     </row>
